--- a/data/ams_weekly_data/White_Mulberry/ads_report_week35.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week35.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SB" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SB" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1698,10 +1698,10 @@
         <v>4754</v>
       </c>
       <c r="G45" t="n">
-        <v>1066.1</v>
+        <v>1599.15</v>
       </c>
       <c r="H45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -3843,7 +3843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4269,186 +4269,21 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>28</v>
+        <v>166</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F13" t="n">
-        <v>6.091666666666666</v>
+        <v>36.55</v>
       </c>
       <c r="G13" t="n">
-        <v>758.5533333333333</v>
+        <v>4551.32</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>B0DB5VVPSB</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>28</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" t="n">
-        <v>6.091666666666666</v>
-      </c>
-      <c r="G14" t="n">
-        <v>758.5533333333333</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>B0DB5W4TCP</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>28</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" t="n">
-        <v>6.091666666666666</v>
-      </c>
-      <c r="G15" t="n">
-        <v>758.5533333333333</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>B0DB5YTQZV</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>28</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" t="n">
-        <v>6.091666666666666</v>
-      </c>
-      <c r="G16" t="n">
-        <v>758.5533333333333</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>B0DP2Z5DQ9</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>28</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" t="n">
-        <v>6.091666666666666</v>
-      </c>
-      <c r="G17" t="n">
-        <v>758.5533333333333</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>B0DP32F346</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>28</v>
-      </c>
-      <c r="E18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" t="n">
-        <v>6.091666666666666</v>
-      </c>
-      <c r="G18" t="n">
-        <v>758.5533333333333</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="inlineStr">
         <is>
           <t>White Mulberry</t>
         </is>
